--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.73775421654271</v>
+        <v>4.83238506018819</v>
       </c>
       <c r="D2" t="n">
-        <v>29.46618102969384</v>
+        <v>4.788254417325248</v>
       </c>
       <c r="E2" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F2" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33034383038123</v>
+        <v>3.30368087243695</v>
       </c>
       <c r="D3" t="n">
-        <v>19.96541486151891</v>
+        <v>3.244379914996824</v>
       </c>
       <c r="E3" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F3" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.185034895654409</v>
+        <v>1.005068170543842</v>
       </c>
       <c r="D4" t="n">
-        <v>5.670644253094085</v>
+        <v>0.9214796911277889</v>
       </c>
       <c r="E4" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F4" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.7542642045676</v>
+        <v>4.510067933242236</v>
       </c>
       <c r="D5" t="n">
-        <v>27.2183157467726</v>
+        <v>4.422976308850548</v>
       </c>
       <c r="E5" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F5" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.93393403141981</v>
+        <v>3.239264280105719</v>
       </c>
       <c r="D6" t="n">
-        <v>20.36949599174237</v>
+        <v>3.310043098658136</v>
       </c>
       <c r="E6" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F6" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.842865490095773</v>
+        <v>1.599465642140563</v>
       </c>
       <c r="D7" t="n">
-        <v>9.507395148610279</v>
+        <v>1.54495171164917</v>
       </c>
       <c r="E7" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F7" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.92697524858842</v>
+        <v>2.100633477895617</v>
       </c>
       <c r="D8" t="n">
-        <v>12.72041973075467</v>
+        <v>2.067068206247634</v>
       </c>
       <c r="E8" t="n">
-        <v>8.227885678510486</v>
+        <v>1.337031422757954</v>
       </c>
       <c r="F8" t="n">
-        <v>8.261546466119102</v>
+        <v>1.342501300744354</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
